--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="714">
   <si>
     <t/>
   </si>
@@ -2033,12 +2033,6 @@
   </si>
   <si>
     <t>IDM M/GORENG 2L</t>
-  </si>
-  <si>
-    <t>20043943</t>
-  </si>
-  <si>
-    <t>LARISST M/GORENG 2L</t>
   </si>
   <si>
     <t>10012338</t>
@@ -2551,7 +2545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F334"/>
+  <dimension ref="A1:F333"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -8872,30 +8866,30 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>443</v>
+        <v>15</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D317" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>678</v>
-      </c>
       <c r="E317" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>15</v>
@@ -8912,13 +8906,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8932,10 +8926,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>84</v>
@@ -8952,13 +8946,13 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -8972,13 +8966,13 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8992,30 +8986,30 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D323" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="E323" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>84</v>
@@ -9032,10 +9026,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>84</v>
@@ -9052,10 +9046,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>84</v>
@@ -9072,10 +9066,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>84</v>
@@ -9092,10 +9086,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9112,10 +9106,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9123,19 +9117,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>704</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9152,10 +9146,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9172,13 +9166,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9192,10 +9186,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>15</v>
@@ -9203,41 +9197,21 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>713</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="E334" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F334" s="1" t="s">
         <v>84</v>
       </c>
     </row>
